--- a/1-data/TableS2.xlsx
+++ b/1-data/TableS2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -379,23 +379,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>f__Alcaligenaceae</t>
+          <t>Acidaminococcaceae</t>
         </is>
       </c>
       <c r="B2">
-        <v>168</v>
+        <v>63</v>
       </c>
       <c r="C2">
-        <v>0.9216376268957175</v>
+        <v>0.843146226160145</v>
       </c>
       <c r="D2">
-        <v>3.81836788233267E-70</v>
+        <v>4.375237086511562E-18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>f__Bacillaceae</t>
+          <t>Akkermansiaceae</t>
         </is>
       </c>
       <c r="B3">
@@ -405,391 +405,477 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>f__Bacteroidaceae</t>
+          <t>Anaerovoracaceae</t>
         </is>
       </c>
       <c r="B4">
-        <v>1227</v>
+        <v>58</v>
       </c>
       <c r="C4">
-        <v>0.9387228135179511</v>
+        <v>0.8871337317560811</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1.862883056528125E-20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>f__Bifidobacteriaceae</t>
+          <t>Bacillaceae</t>
         </is>
       </c>
       <c r="B5">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>0.1663862400663275</v>
-      </c>
-      <c r="D5">
-        <v>0.645940111078992</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>f__Clostridiaceae</t>
+          <t>Bacteroidaceae</t>
         </is>
       </c>
       <c r="B6">
-        <v>248</v>
+        <v>1096</v>
       </c>
       <c r="C6">
-        <v>0.9422323548501894</v>
+        <v>0.9430853988115283</v>
       </c>
       <c r="D6">
-        <v>7.584230320981243E-119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>f__Coriobacteriaceae</t>
+          <t>Barnesiellaceae</t>
         </is>
       </c>
       <c r="B7">
-        <v>218</v>
+        <v>102</v>
       </c>
       <c r="C7">
-        <v>0.8756782586795234</v>
+        <v>0.3379793645795326</v>
       </c>
       <c r="D7">
-        <v>3.18748789630783E-70</v>
+        <v>0.0005124196568817213</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>f__Desulfovibrionaceae</t>
+          <t>Bifidobacteriaceae</t>
         </is>
       </c>
       <c r="B8">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>0.5996707871205558</v>
+        <v>0.4069892089395035</v>
       </c>
       <c r="D8">
-        <v>1.694671799540297E-05</v>
+        <v>0.3169750464900298</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>f__Enterobacteriaceae</t>
+          <t>Butyricicoccaceae</t>
         </is>
       </c>
       <c r="B9">
-        <v>3056</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>0.9703262328300104</v>
+        <v>0.8622086911862334</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>4.202297887044791E-06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f__Enterococcaceae</t>
+          <t>Clostridiaceae</t>
         </is>
       </c>
       <c r="B10">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="C10">
-        <v>0.7823336342514898</v>
+        <v>0.9476816080799042</v>
       </c>
       <c r="D10">
-        <v>1.581715970714502E-53</v>
+        <v>1.514979585719061E-115</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f__Erysipelotrichaceae</t>
+          <t>Coriobacteriaceae</t>
         </is>
       </c>
       <c r="B11">
-        <v>317</v>
+        <v>92</v>
       </c>
       <c r="C11">
-        <v>0.9039221983430165</v>
+        <v>0.8256192550498515</v>
       </c>
       <c r="D11">
-        <v>3.190678359174575E-118</v>
+        <v>4.320636529178605E-24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f__Eubacteriaceae</t>
+          <t>Desulfovibrionaceae</t>
         </is>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C12">
-        <v>-0.9309427311292509</v>
+        <v>0.6494315606913658</v>
       </c>
       <c r="D12">
-        <v>0.2379750047237256</v>
+        <v>3.270308726401663E-06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>f__Lachnospiraceae</t>
+          <t>Eggerthellaceae</t>
         </is>
       </c>
       <c r="B13">
-        <v>1341</v>
+        <v>119</v>
       </c>
       <c r="C13">
-        <v>0.8935734518477363</v>
+        <v>0.8370410978643822</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1.995946226313582E-32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>f__Lactobacillaceae</t>
+          <t>Enterobacteriaceae</t>
         </is>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>421</v>
+      </c>
+      <c r="C14">
+        <v>0.9762489838349104</v>
+      </c>
+      <c r="D14">
+        <v>1.928457782837931E-280</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>f__Peptococcaceae</t>
+          <t>Enterococcaceae</t>
         </is>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>233</v>
+      </c>
+      <c r="C15">
+        <v>0.7467114382657638</v>
+      </c>
+      <c r="D15">
+        <v>8.693371941672875E-43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>f__Peptostreptococcaceae</t>
+          <t>Erysipelatoclostridiaceae</t>
         </is>
       </c>
       <c r="B16">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="C16">
-        <v>0.9471248568232076</v>
+        <v>0.925107342661238</v>
       </c>
       <c r="D16">
-        <v>1.863096891012936E-74</v>
+        <v>8.683096100867644E-85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>f__Planococcaceae</t>
+          <t>Erysipelotrichaceae</t>
         </is>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>69</v>
+      </c>
+      <c r="C17">
+        <v>0.4389686631215571</v>
+      </c>
+      <c r="D17">
+        <v>0.0001611908892868845</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f__Porphyromonadaceae</t>
+          <t>Eubacteriaceae</t>
         </is>
       </c>
       <c r="B18">
-        <v>482</v>
-      </c>
-      <c r="C18">
-        <v>0.8507395301364136</v>
-      </c>
-      <c r="D18">
-        <v>3.471992337371164E-136</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>f__Prevotellaceae</t>
+          <t>Family XI</t>
         </is>
       </c>
       <c r="B19">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="C19">
-        <v>0.9061956845354457</v>
+        <v>0.9190092274080607</v>
       </c>
       <c r="D19">
-        <v>0.0007586301067218109</v>
+        <v>8.368208347064265E-55</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f__Rikenellaceae</t>
+          <t>Lachnospiraceae</t>
         </is>
       </c>
       <c r="B20">
-        <v>8</v>
+        <v>1245</v>
       </c>
       <c r="C20">
-        <v>-0.5236280554899425</v>
+        <v>0.8538796930215743</v>
       </c>
       <c r="D20">
-        <v>0.1828999507983859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f__Ruminococcaceae</t>
+          <t>Lactobacillaceae</t>
         </is>
       </c>
       <c r="B21">
-        <v>359</v>
-      </c>
-      <c r="C21">
-        <v>0.881268753713105</v>
-      </c>
-      <c r="D21">
-        <v>3.014246690139377E-118</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>f__Streptococcaceae</t>
+          <t>Marinifilaceae</t>
         </is>
       </c>
       <c r="B22">
-        <v>184</v>
-      </c>
-      <c r="C22">
-        <v>0.9647992549437189</v>
-      </c>
-      <c r="D22">
-        <v>1.640096297997828E-107</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>f__Veillonellaceae</t>
+          <t>Morganellaceae</t>
         </is>
       </c>
       <c r="B23">
-        <v>515</v>
+        <v>162</v>
       </c>
       <c r="C23">
-        <v>0.9182884190698526</v>
+        <v>0.9943775492079412</v>
       </c>
       <c r="D23">
-        <v>1.418069136575424E-208</v>
+        <v>6.029245493149503E-158</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>f__Verrucomicrobiaceae</t>
+          <t>Oscillospiraceae</t>
         </is>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>225</v>
+      </c>
+      <c r="C24">
+        <v>0.8942306607105354</v>
+      </c>
+      <c r="D24">
+        <v>8.418791818492952E-80</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>f__[Barnesiellaceae]</t>
+          <t>Paenibacillaceae</t>
         </is>
       </c>
       <c r="B25">
-        <v>104</v>
-      </c>
-      <c r="C25">
-        <v>0.3005020552925285</v>
-      </c>
-      <c r="D25">
-        <v>0.001938733171911658</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>f__[Mogibacteriaceae]</t>
+          <t>Peptostreptococcaceae</t>
         </is>
       </c>
       <c r="B26">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="C26">
-        <v>0.9104912103069003</v>
+        <v>0.9522831892183834</v>
       </c>
       <c r="D26">
-        <v>2.150684791809002E-27</v>
+        <v>4.94329423354547E-74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>f__[Odoribacteraceae]</t>
+          <t>Porphyromonadaceae</t>
         </is>
       </c>
       <c r="B27">
-        <v>9</v>
+        <v>107</v>
+      </c>
+      <c r="C27">
+        <v>0.9270386569031911</v>
+      </c>
+      <c r="D27">
+        <v>1.554792516611282E-46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>f__[Paraprevotellaceae]</t>
+          <t>Prevotellaceae</t>
         </is>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="C28">
+        <v>0.5211599314207228</v>
+      </c>
+      <c r="D28">
+        <v>0.05599791113913691</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>f__[Tissierellaceae]</t>
+          <t>Rikenellaceae</t>
         </is>
       </c>
       <c r="B29">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>0.9167721507122083</v>
+        <v>-0.7658513653603353</v>
       </c>
       <c r="D29">
-        <v>1.15751380285598E-59</v>
+        <v>0.0447108846105418</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>o: Clostridiales</t>
+          <t>Ruminococcaceae</t>
         </is>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>44</v>
+      </c>
+      <c r="C30">
+        <v>0.8612209071265874</v>
+      </c>
+      <c r="D30">
+        <v>6.365056200900977E-14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Selenomonadaceae</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Streptococcaceae</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>137</v>
+      </c>
+      <c r="C32">
+        <v>0.9691867381999169</v>
+      </c>
+      <c r="D32">
+        <v>5.052610573167997E-84</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sutterellaceae</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>150</v>
+      </c>
+      <c r="C33">
+        <v>0.9210743882111543</v>
+      </c>
+      <c r="D33">
+        <v>1.689130664533791E-62</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tannerellaceae</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>330</v>
+      </c>
+      <c r="C34">
+        <v>0.7341842943114603</v>
+      </c>
+      <c r="D34">
+        <v>4.164799140172586E-57</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Veillonellaceae</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>390</v>
+      </c>
+      <c r="C35">
+        <v>0.947656981546275</v>
+      </c>
+      <c r="D35">
+        <v>1.796745413734865E-194</v>
       </c>
     </row>
   </sheetData>
